--- a/experiments/prompt-tuning/hc+ft/Results/Cardd_qwen_greedy/cardd_prompt04.xlsx
+++ b/experiments/prompt-tuning/hc+ft/Results/Cardd_qwen_greedy/cardd_prompt04.xlsx
@@ -1,15 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="20417"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\UshariRanasinghe\Desktop\Projects\vlm-research\experiments\prompt-tuning\hc+ft\Results\Cardd_qwen_greedy\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD9E831E-4010-4EDE-956F-2139541DF7DB}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView minimized="1" xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6810" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="evaluation" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
@@ -109,8 +115,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -173,6 +179,14 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -193,7 +207,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1" descr="image_1.png"/>
+        <xdr:cNvPr id="2" name="Picture 1" descr="image_1.png">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -231,7 +251,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Picture 2" descr="image_2.png"/>
+        <xdr:cNvPr id="3" name="Picture 2" descr="image_2.png">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000003000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -269,7 +295,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="Picture 3" descr="image_3.png"/>
+        <xdr:cNvPr id="4" name="Picture 3" descr="image_3.png">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000004000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -307,7 +339,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="Picture 4" descr="image_4.png"/>
+        <xdr:cNvPr id="5" name="Picture 4" descr="image_4.png">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000005000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -345,7 +383,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="6" name="Picture 5" descr="image_5.png"/>
+        <xdr:cNvPr id="6" name="Picture 5" descr="image_5.png">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000006000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -383,7 +427,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="7" name="Picture 6" descr="image_6.png"/>
+        <xdr:cNvPr id="7" name="Picture 6" descr="image_6.png">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000007000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -421,7 +471,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="8" name="Picture 7" descr="image_7.png"/>
+        <xdr:cNvPr id="8" name="Picture 7" descr="image_7.png">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000008000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -459,7 +515,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="9" name="Picture 8" descr="image_8.png"/>
+        <xdr:cNvPr id="9" name="Picture 8" descr="image_8.png">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000009000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -497,7 +559,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="10" name="Picture 9" descr="image_9.png"/>
+        <xdr:cNvPr id="10" name="Picture 9" descr="image_9.png">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000A000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -535,7 +603,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="11" name="Picture 10" descr="image_10.png"/>
+        <xdr:cNvPr id="11" name="Picture 10" descr="image_10.png">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000B000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -604,7 +678,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -636,9 +710,27 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -670,6 +762,24 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -845,11 +955,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="B1:J11"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="B1:J12"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="2:10">
+    <row r="1" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -878,7 +988,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="2:10">
+    <row r="2" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B2">
         <v>0</v>
       </c>
@@ -892,22 +1002,22 @@
         <v>20</v>
       </c>
       <c r="F2">
-        <v>0.8864048719406128</v>
+        <v>0.88640487194061279</v>
       </c>
       <c r="G2">
-        <v>0.3508771929824561</v>
+        <v>0.35087719298245612</v>
       </c>
       <c r="H2">
-        <v>2.875970342796281</v>
+        <v>2.8759703427962808</v>
       </c>
       <c r="I2">
         <v>7103.908203125</v>
       </c>
       <c r="J2">
-        <v>17.37897539138794</v>
+        <v>17.378975391387939</v>
       </c>
     </row>
-    <row r="3" spans="2:10">
+    <row r="3" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B3">
         <v>1</v>
       </c>
@@ -921,10 +1031,10 @@
         <v>21</v>
       </c>
       <c r="F3">
-        <v>0.8046932220458984</v>
+        <v>0.80469322204589844</v>
       </c>
       <c r="G3">
-        <v>0.2926829268292683</v>
+        <v>0.29268292682926828</v>
       </c>
       <c r="H3">
         <v>3.126274846143315</v>
@@ -933,10 +1043,10 @@
         <v>7112.033203125</v>
       </c>
       <c r="J3">
-        <v>5.363538026809692</v>
+        <v>5.3635380268096924</v>
       </c>
     </row>
-    <row r="4" spans="2:10">
+    <row r="4" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B4">
         <v>2</v>
       </c>
@@ -950,7 +1060,7 @@
         <v>22</v>
       </c>
       <c r="F4">
-        <v>0.675227165222168</v>
+        <v>0.67522716522216797</v>
       </c>
       <c r="G4">
         <v>0.1851851851851852</v>
@@ -962,10 +1072,10 @@
         <v>7112.033203125</v>
       </c>
       <c r="J4">
-        <v>5.725734710693359</v>
+        <v>5.7257347106933594</v>
       </c>
     </row>
-    <row r="5" spans="2:10">
+    <row r="5" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B5">
         <v>3</v>
       </c>
@@ -979,22 +1089,22 @@
         <v>23</v>
       </c>
       <c r="F5">
-        <v>0.7943471074104309</v>
+        <v>0.79434710741043091</v>
       </c>
       <c r="G5">
-        <v>0.2758620689655172</v>
+        <v>0.27586206896551718</v>
       </c>
       <c r="H5">
-        <v>2.243402194522061</v>
+        <v>2.2434021945220608</v>
       </c>
       <c r="I5">
         <v>7141.18896484375</v>
       </c>
       <c r="J5">
-        <v>5.524040222167969</v>
+        <v>5.5240402221679688</v>
       </c>
     </row>
-    <row r="6" spans="2:10">
+    <row r="6" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B6">
         <v>4</v>
       </c>
@@ -1008,22 +1118,22 @@
         <v>24</v>
       </c>
       <c r="F6">
-        <v>0.5003074407577515</v>
+        <v>0.50030744075775146</v>
       </c>
       <c r="G6">
-        <v>0.09523809523809523</v>
+        <v>9.5238095238095233E-2</v>
       </c>
       <c r="H6">
-        <v>1.370684376053528</v>
+        <v>1.3706843760535281</v>
       </c>
       <c r="I6">
         <v>7118.03125</v>
       </c>
       <c r="J6">
-        <v>5.951688051223755</v>
+        <v>5.9516880512237549</v>
       </c>
     </row>
-    <row r="7" spans="2:10">
+    <row r="7" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B7">
         <v>5</v>
       </c>
@@ -1037,22 +1147,22 @@
         <v>25</v>
       </c>
       <c r="F7">
-        <v>0.6760613322257996</v>
+        <v>0.67606133222579956</v>
       </c>
       <c r="G7">
-        <v>0.1621621621621621</v>
+        <v>0.16216216216216209</v>
       </c>
       <c r="H7">
-        <v>1.708783605720881</v>
+        <v>1.7087836057208809</v>
       </c>
       <c r="I7">
         <v>7118.03125</v>
       </c>
       <c r="J7">
-        <v>4.023722410202026</v>
+        <v>4.0237224102020264</v>
       </c>
     </row>
-    <row r="8" spans="2:10">
+    <row r="8" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B8">
         <v>6</v>
       </c>
@@ -1066,10 +1176,10 @@
         <v>26</v>
       </c>
       <c r="F8">
-        <v>0.8398033976554871</v>
+        <v>0.83980339765548706</v>
       </c>
       <c r="G8">
-        <v>0.2571428571428572</v>
+        <v>0.25714285714285717</v>
       </c>
       <c r="H8">
         <v>2.569570238645106</v>
@@ -1081,7 +1191,7 @@
         <v>6.288689136505127</v>
       </c>
     </row>
-    <row r="9" spans="2:10">
+    <row r="9" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B9">
         <v>7</v>
       </c>
@@ -1095,22 +1205,22 @@
         <v>27</v>
       </c>
       <c r="F9">
-        <v>0.9002517461776733</v>
+        <v>0.90025174617767334</v>
       </c>
       <c r="G9">
-        <v>0.4615384615384615</v>
+        <v>0.46153846153846151</v>
       </c>
       <c r="H9">
-        <v>3.462048706043676</v>
+        <v>3.4620487060436762</v>
       </c>
       <c r="I9">
         <v>7109.9697265625</v>
       </c>
       <c r="J9">
-        <v>3.698195934295654</v>
+        <v>3.6981959342956539</v>
       </c>
     </row>
-    <row r="10" spans="2:10">
+    <row r="10" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B10">
         <v>8</v>
       </c>
@@ -1124,22 +1234,22 @@
         <v>28</v>
       </c>
       <c r="F10">
-        <v>0.8274801969528198</v>
+        <v>0.82748019695281982</v>
       </c>
       <c r="G10">
-        <v>0.2307692307692308</v>
+        <v>0.23076923076923081</v>
       </c>
       <c r="H10">
-        <v>2.656327640464191</v>
+        <v>2.6563276404641911</v>
       </c>
       <c r="I10">
         <v>7141.18896484375</v>
       </c>
       <c r="J10">
-        <v>4.692915439605713</v>
+        <v>4.6929154396057129</v>
       </c>
     </row>
-    <row r="11" spans="2:10">
+    <row r="11" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B11">
         <v>9</v>
       </c>
@@ -1153,10 +1263,10 @@
         <v>29</v>
       </c>
       <c r="F11">
-        <v>0.7258853316307068</v>
+        <v>0.72588533163070679</v>
       </c>
       <c r="G11">
-        <v>0.2647058823529412</v>
+        <v>0.26470588235294118</v>
       </c>
       <c r="H11">
         <v>3.289251797469364</v>
@@ -1165,7 +1275,29 @@
         <v>7141.18896484375</v>
       </c>
       <c r="J11">
-        <v>4.638728380203247</v>
+        <v>4.6387283802032471</v>
+      </c>
+    </row>
+    <row r="12" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="F12">
+        <f>AVERAGE(F3:F11)</f>
+        <v>0.74933966000874841</v>
+      </c>
+      <c r="G12">
+        <f t="shared" ref="G12:J12" si="0">AVERAGE(G3:G11)</f>
+        <v>0.24725409668707984</v>
+      </c>
+      <c r="H12">
+        <f t="shared" si="0"/>
+        <v>2.5714902119992398</v>
+      </c>
+      <c r="I12">
+        <f t="shared" si="0"/>
+        <v>7123.5218641493057</v>
+      </c>
+      <c r="J12">
+        <f t="shared" si="0"/>
+        <v>5.1008058124118385</v>
       </c>
     </row>
   </sheetData>
